--- a/test_set/results/eval_outputs/master_comparison.xlsx
+++ b/test_set/results/eval_outputs/master_comparison.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -102,6 +102,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -469,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:S37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -483,6 +486,14 @@
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -496,6 +507,16 @@
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
+          <t>Llama</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
           <t>Qwen</t>
         </is>
       </c>
@@ -506,10 +527,20 @@
       <c r="C2" s="1" t="n"/>
       <c r="D2" s="3" t="inlineStr">
         <is>
+          <t>small</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>small</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
@@ -571,6 +602,46 @@
           <t>token_precision</t>
         </is>
       </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>token_recall</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>precision</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>token_precision</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>token_recall</t>
+        </is>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>precision</t>
+        </is>
+      </c>
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>token_precision</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -589,27 +660,51 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>0.622</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="H4" s="6" t="n">
         <v>0.019</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="I4" s="6" t="n">
         <v>0.038</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="J4" s="6" t="n">
         <v>0.8</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="K4" s="6" t="n">
         <v>0.08400000000000001</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="L4" s="6" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="M4" s="6" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="N4" s="6" t="n">
+        <v>0.458</v>
+      </c>
+      <c r="O4" s="6" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="P4" s="6" t="n">
         <v>0.185</v>
       </c>
-      <c r="I4" s="6" t="n">
+      <c r="Q4" s="6" t="n">
         <v>0.22</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="R4" s="6" t="n">
         <v>0.628</v>
       </c>
-      <c r="K4" s="6" t="n">
+      <c r="S4" s="6" t="n">
         <v>0.187</v>
       </c>
     </row>
@@ -622,27 +717,51 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>0.432</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="H5" s="6" t="n">
         <v>0.023</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="I5" s="6" t="n">
         <v>0.04</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="J5" s="6" t="n">
         <v>0.7</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="K5" s="6" t="n">
         <v>0.08500000000000001</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="L5" s="6" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="M5" s="6" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="N5" s="6" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="O5" s="6" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="P5" s="6" t="n">
         <v>0.268</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="Q5" s="6" t="n">
         <v>0.362</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="R5" s="6" t="n">
         <v>0.605</v>
       </c>
-      <c r="K5" s="6" t="n">
+      <c r="S5" s="6" t="n">
         <v>0.196</v>
       </c>
     </row>
@@ -655,27 +774,51 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>0.432</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="H6" s="6" t="n">
         <v>0.023</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="I6" s="6" t="n">
         <v>0.04</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="J6" s="6" t="n">
         <v>0.7</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="K6" s="6" t="n">
         <v>0.08500000000000001</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="L6" s="6" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="M6" s="6" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="N6" s="6" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="O6" s="6" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="P6" s="6" t="n">
         <v>0.268</v>
       </c>
-      <c r="I6" s="6" t="n">
+      <c r="Q6" s="6" t="n">
         <v>0.362</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="R6" s="6" t="n">
         <v>0.605</v>
       </c>
-      <c r="K6" s="6" t="n">
+      <c r="S6" s="6" t="n">
         <v>0.196</v>
       </c>
     </row>
@@ -692,27 +835,51 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="H7" s="6" t="n">
         <v>0.116</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="I7" s="6" t="n">
         <v>0.267</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="J7" s="6" t="n">
         <v>0.8090000000000001</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="K7" s="6" t="n">
         <v>0.123</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="L7" s="6" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="M7" s="6" t="n">
+        <v>0.257</v>
+      </c>
+      <c r="N7" s="6" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="O7" s="6" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="P7" s="6" t="n">
         <v>0.359</v>
       </c>
-      <c r="I7" s="6" t="n">
+      <c r="Q7" s="6" t="n">
         <v>0.5590000000000001</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="R7" s="6" t="n">
         <v>0.616</v>
       </c>
-      <c r="K7" s="6" t="n">
+      <c r="S7" s="6" t="n">
         <v>0.154</v>
       </c>
     </row>
@@ -725,27 +892,51 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="H8" s="6" t="n">
         <v>0.116</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="I8" s="6" t="n">
         <v>0.267</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="J8" s="6" t="n">
         <v>0.8090000000000001</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="K8" s="6" t="n">
         <v>0.123</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="L8" s="6" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="M8" s="6" t="n">
+        <v>0.257</v>
+      </c>
+      <c r="N8" s="6" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="O8" s="6" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="P8" s="6" t="n">
         <v>0.36</v>
       </c>
-      <c r="I8" s="6" t="n">
+      <c r="Q8" s="6" t="n">
         <v>0.5610000000000001</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="R8" s="6" t="n">
         <v>0.615</v>
       </c>
-      <c r="K8" s="6" t="n">
+      <c r="S8" s="6" t="n">
         <v>0.154</v>
       </c>
     </row>
@@ -758,27 +949,51 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="H9" s="6" t="n">
         <v>0.116</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="I9" s="6" t="n">
         <v>0.267</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="J9" s="6" t="n">
         <v>0.8090000000000001</v>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="K9" s="6" t="n">
         <v>0.123</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="L9" s="6" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="M9" s="6" t="n">
+        <v>0.257</v>
+      </c>
+      <c r="N9" s="6" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="O9" s="6" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="P9" s="6" t="n">
         <v>0.36</v>
       </c>
-      <c r="I9" s="6" t="n">
+      <c r="Q9" s="6" t="n">
         <v>0.5610000000000001</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="R9" s="6" t="n">
         <v>0.615</v>
       </c>
-      <c r="K9" s="6" t="n">
+      <c r="S9" s="6" t="n">
         <v>0.154</v>
       </c>
     </row>
@@ -799,27 +1014,51 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>0.258</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H10" s="6" t="n">
         <v>0.043</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="I10" s="6" t="n">
         <v>0.027</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="J10" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="K10" s="6" t="n">
         <v>0.483</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="L10" s="6" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="M10" s="6" t="n">
+        <v>0.116</v>
+      </c>
+      <c r="N10" s="6" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="O10" s="6" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="P10" s="6" t="n">
         <v>0.127</v>
       </c>
-      <c r="I10" s="6" t="n">
+      <c r="Q10" s="6" t="n">
         <v>0.14</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="R10" s="6" t="n">
         <v>0.594</v>
       </c>
-      <c r="K10" s="6" t="n">
+      <c r="S10" s="6" t="n">
         <v>0.219</v>
       </c>
     </row>
@@ -832,27 +1071,51 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="H11" s="6" t="n">
         <v>0.064</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="I11" s="6" t="n">
         <v>0.054</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="J11" s="6" t="n">
         <v>0.494</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="K11" s="6" t="n">
         <v>0.475</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="L11" s="6" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="M11" s="6" t="n">
+        <v>0.149</v>
+      </c>
+      <c r="N11" s="6" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="O11" s="6" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="P11" s="6" t="n">
         <v>0.246</v>
       </c>
-      <c r="I11" s="6" t="n">
+      <c r="Q11" s="6" t="n">
         <v>0.315</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="R11" s="6" t="n">
         <v>0.556</v>
       </c>
-      <c r="K11" s="6" t="n">
+      <c r="S11" s="6" t="n">
         <v>0.205</v>
       </c>
     </row>
@@ -865,27 +1128,51 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="H12" s="6" t="n">
         <v>0.064</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="I12" s="6" t="n">
         <v>0.054</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="J12" s="6" t="n">
         <v>0.494</v>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="K12" s="6" t="n">
         <v>0.475</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="L12" s="6" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="M12" s="6" t="n">
+        <v>0.149</v>
+      </c>
+      <c r="N12" s="6" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="O12" s="6" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="P12" s="6" t="n">
         <v>0.246</v>
       </c>
-      <c r="I12" s="6" t="n">
+      <c r="Q12" s="6" t="n">
         <v>0.315</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="R12" s="6" t="n">
         <v>0.556</v>
       </c>
-      <c r="K12" s="6" t="n">
+      <c r="S12" s="6" t="n">
         <v>0.205</v>
       </c>
     </row>
@@ -902,27 +1189,51 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.242</v>
+      </c>
+      <c r="H13" s="6" t="n">
         <v>0.096</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="I13" s="6" t="n">
         <v>0.068</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="J13" s="6" t="n">
         <v>0.411</v>
       </c>
-      <c r="G13" s="6" t="n">
+      <c r="K13" s="6" t="n">
         <v>0.188</v>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="L13" s="6" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="M13" s="6" t="n">
+        <v>0.207</v>
+      </c>
+      <c r="N13" s="6" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="O13" s="6" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="P13" s="6" t="n">
         <v>0.293</v>
       </c>
-      <c r="I13" s="6" t="n">
+      <c r="Q13" s="6" t="n">
         <v>0.322</v>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="R13" s="6" t="n">
         <v>0.427</v>
       </c>
-      <c r="K13" s="6" t="n">
+      <c r="S13" s="6" t="n">
         <v>0.232</v>
       </c>
     </row>
@@ -935,27 +1246,51 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H14" s="6" t="n">
         <v>0.137</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="I14" s="6" t="n">
         <v>0.121</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="J14" s="6" t="n">
         <v>0.362</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="K14" s="6" t="n">
         <v>0.179</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="L14" s="6" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="M14" s="6" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="N14" s="6" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="O14" s="6" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="P14" s="6" t="n">
         <v>0.317</v>
       </c>
-      <c r="I14" s="6" t="n">
+      <c r="Q14" s="6" t="n">
         <v>0.365</v>
       </c>
-      <c r="J14" s="6" t="n">
+      <c r="R14" s="6" t="n">
         <v>0.429</v>
       </c>
-      <c r="K14" s="6" t="n">
+      <c r="S14" s="6" t="n">
         <v>0.243</v>
       </c>
     </row>
@@ -968,27 +1303,51 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H15" s="6" t="n">
         <v>0.137</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="I15" s="6" t="n">
         <v>0.121</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="J15" s="6" t="n">
         <v>0.362</v>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="K15" s="6" t="n">
         <v>0.179</v>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="L15" s="6" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="M15" s="6" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="N15" s="6" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="O15" s="6" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="P15" s="6" t="n">
         <v>0.317</v>
       </c>
-      <c r="I15" s="6" t="n">
+      <c r="Q15" s="6" t="n">
         <v>0.365</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="R15" s="6" t="n">
         <v>0.429</v>
       </c>
-      <c r="K15" s="6" t="n">
+      <c r="S15" s="6" t="n">
         <v>0.243</v>
       </c>
     </row>
@@ -1009,27 +1368,51 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>0.253</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.251</v>
+      </c>
+      <c r="H16" s="6" t="n">
         <v>0.109</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="I16" s="6" t="n">
         <v>0.067</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="J16" s="6" t="n">
         <v>0.41</v>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="K16" s="6" t="n">
         <v>0.28</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="L16" s="6" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="M16" s="6" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="N16" s="6" t="n">
+        <v>0.212</v>
+      </c>
+      <c r="O16" s="6" t="n">
+        <v>0.164</v>
+      </c>
+      <c r="P16" s="6" t="n">
         <v>0.232</v>
       </c>
-      <c r="I16" s="6" t="n">
+      <c r="Q16" s="6" t="n">
         <v>0.21</v>
       </c>
-      <c r="J16" s="6" t="n">
+      <c r="R16" s="6" t="n">
         <v>0.456</v>
       </c>
-      <c r="K16" s="6" t="n">
+      <c r="S16" s="6" t="n">
         <v>0.294</v>
       </c>
     </row>
@@ -1042,27 +1425,51 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H17" s="6" t="n">
         <v>0.124</v>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="I17" s="6" t="n">
         <v>0.08599999999999999</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="J17" s="6" t="n">
         <v>0.391</v>
       </c>
-      <c r="G17" s="6" t="n">
+      <c r="K17" s="6" t="n">
         <v>0.253</v>
       </c>
-      <c r="H17" s="6" t="n">
+      <c r="L17" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="M17" s="6" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="N17" s="6" t="n">
+        <v>0.204</v>
+      </c>
+      <c r="O17" s="6" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="P17" s="6" t="n">
         <v>0.259</v>
       </c>
-      <c r="I17" s="6" t="n">
+      <c r="Q17" s="6" t="n">
         <v>0.242</v>
       </c>
-      <c r="J17" s="6" t="n">
+      <c r="R17" s="6" t="n">
         <v>0.44</v>
       </c>
-      <c r="K17" s="6" t="n">
+      <c r="S17" s="6" t="n">
         <v>0.27</v>
       </c>
     </row>
@@ -1075,27 +1482,51 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H18" s="6" t="n">
         <v>0.124</v>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="I18" s="6" t="n">
         <v>0.08599999999999999</v>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="J18" s="6" t="n">
         <v>0.391</v>
       </c>
-      <c r="G18" s="6" t="n">
+      <c r="K18" s="6" t="n">
         <v>0.253</v>
       </c>
-      <c r="H18" s="6" t="n">
+      <c r="L18" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="M18" s="6" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="N18" s="6" t="n">
+        <v>0.204</v>
+      </c>
+      <c r="O18" s="6" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="P18" s="6" t="n">
         <v>0.259</v>
       </c>
-      <c r="I18" s="6" t="n">
+      <c r="Q18" s="6" t="n">
         <v>0.242</v>
       </c>
-      <c r="J18" s="6" t="n">
+      <c r="R18" s="6" t="n">
         <v>0.44</v>
       </c>
-      <c r="K18" s="6" t="n">
+      <c r="S18" s="6" t="n">
         <v>0.27</v>
       </c>
     </row>
@@ -1112,27 +1543,51 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="H19" s="6" t="n">
         <v>0.103</v>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="I19" s="6" t="n">
         <v>0.059</v>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="J19" s="6" t="n">
         <v>0.33</v>
       </c>
-      <c r="G19" s="6" t="n">
+      <c r="K19" s="6" t="n">
         <v>0.291</v>
       </c>
-      <c r="H19" s="6" t="n">
+      <c r="L19" s="6" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="M19" s="6" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="N19" s="6" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="O19" s="6" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="P19" s="6" t="n">
         <v>0.209</v>
       </c>
-      <c r="I19" s="6" t="n">
+      <c r="Q19" s="6" t="n">
         <v>0.189</v>
       </c>
-      <c r="J19" s="6" t="n">
+      <c r="R19" s="6" t="n">
         <v>0.394</v>
       </c>
-      <c r="K19" s="6" t="n">
+      <c r="S19" s="6" t="n">
         <v>0.284</v>
       </c>
     </row>
@@ -1145,27 +1600,51 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="H20" s="6" t="n">
         <v>0.117</v>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="I20" s="6" t="n">
         <v>0.077</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="J20" s="6" t="n">
         <v>0.312</v>
       </c>
-      <c r="G20" s="6" t="n">
+      <c r="K20" s="6" t="n">
         <v>0.225</v>
       </c>
-      <c r="H20" s="6" t="n">
+      <c r="L20" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="M20" s="6" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="N20" s="6" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="O20" s="6" t="n">
+        <v>0.204</v>
+      </c>
+      <c r="P20" s="6" t="n">
         <v>0.212</v>
       </c>
-      <c r="I20" s="6" t="n">
+      <c r="Q20" s="6" t="n">
         <v>0.192</v>
       </c>
-      <c r="J20" s="6" t="n">
+      <c r="R20" s="6" t="n">
         <v>0.398</v>
       </c>
-      <c r="K20" s="6" t="n">
+      <c r="S20" s="6" t="n">
         <v>0.287</v>
       </c>
     </row>
@@ -1178,27 +1657,51 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="H21" s="6" t="n">
         <v>0.117</v>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="I21" s="6" t="n">
         <v>0.077</v>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="J21" s="6" t="n">
         <v>0.312</v>
       </c>
-      <c r="G21" s="6" t="n">
+      <c r="K21" s="6" t="n">
         <v>0.225</v>
       </c>
-      <c r="H21" s="6" t="n">
+      <c r="L21" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="M21" s="6" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="N21" s="6" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="O21" s="6" t="n">
+        <v>0.204</v>
+      </c>
+      <c r="P21" s="6" t="n">
         <v>0.212</v>
       </c>
-      <c r="I21" s="6" t="n">
+      <c r="Q21" s="6" t="n">
         <v>0.192</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="R21" s="6" t="n">
         <v>0.398</v>
       </c>
-      <c r="K21" s="6" t="n">
+      <c r="S21" s="6" t="n">
         <v>0.287</v>
       </c>
     </row>
@@ -1219,27 +1722,51 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>0.173</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="H22" s="6" t="n">
         <v>0.161</v>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="I22" s="6" t="n">
         <v>0.114</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="J22" s="6" t="n">
         <v>0.358</v>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="K22" s="6" t="n">
         <v>0.263</v>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="L22" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="M22" s="6" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="N22" s="6" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="O22" s="6" t="n">
+        <v>0.196</v>
+      </c>
+      <c r="P22" s="6" t="n">
         <v>0.203</v>
       </c>
-      <c r="I22" s="6" t="n">
+      <c r="Q22" s="6" t="n">
         <v>0.198</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="R22" s="6" t="n">
         <v>0.35</v>
       </c>
-      <c r="K22" s="6" t="n">
+      <c r="S22" s="6" t="n">
         <v>0.219</v>
       </c>
     </row>
@@ -1252,27 +1779,51 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>0.173</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="H23" s="6" t="n">
         <v>0.169</v>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="I23" s="6" t="n">
         <v>0.125</v>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="J23" s="6" t="n">
         <v>0.358</v>
       </c>
-      <c r="G23" s="6" t="n">
+      <c r="K23" s="6" t="n">
         <v>0.266</v>
       </c>
-      <c r="H23" s="6" t="n">
+      <c r="L23" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="M23" s="6" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="N23" s="6" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="O23" s="6" t="n">
+        <v>0.193</v>
+      </c>
+      <c r="P23" s="6" t="n">
         <v>0.203</v>
       </c>
-      <c r="I23" s="6" t="n">
+      <c r="Q23" s="6" t="n">
         <v>0.198</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="R23" s="6" t="n">
         <v>0.346</v>
       </c>
-      <c r="K23" s="6" t="n">
+      <c r="S23" s="6" t="n">
         <v>0.215</v>
       </c>
     </row>
@@ -1285,27 +1836,51 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>0.173</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="H24" s="6" t="n">
         <v>0.169</v>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="I24" s="6" t="n">
         <v>0.125</v>
       </c>
-      <c r="F24" s="6" t="n">
+      <c r="J24" s="6" t="n">
         <v>0.358</v>
       </c>
-      <c r="G24" s="6" t="n">
+      <c r="K24" s="6" t="n">
         <v>0.266</v>
       </c>
-      <c r="H24" s="6" t="n">
+      <c r="L24" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="M24" s="6" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="N24" s="6" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="O24" s="6" t="n">
+        <v>0.193</v>
+      </c>
+      <c r="P24" s="6" t="n">
         <v>0.203</v>
       </c>
-      <c r="I24" s="6" t="n">
+      <c r="Q24" s="6" t="n">
         <v>0.198</v>
       </c>
-      <c r="J24" s="6" t="n">
+      <c r="R24" s="6" t="n">
         <v>0.346</v>
       </c>
-      <c r="K24" s="6" t="n">
+      <c r="S24" s="6" t="n">
         <v>0.215</v>
       </c>
     </row>
@@ -1322,27 +1897,51 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="H25" s="6" t="n">
         <v>0.183</v>
       </c>
-      <c r="E25" s="6" t="n">
+      <c r="I25" s="6" t="n">
         <v>0.178</v>
       </c>
-      <c r="F25" s="6" t="n">
+      <c r="J25" s="6" t="n">
         <v>0.496</v>
       </c>
-      <c r="G25" s="6" t="n">
+      <c r="K25" s="6" t="n">
         <v>0.182</v>
       </c>
-      <c r="H25" s="6" t="n">
+      <c r="L25" s="6" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="M25" s="6" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="N25" s="6" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="O25" s="6" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="P25" s="6" t="n">
         <v>0.288</v>
       </c>
-      <c r="I25" s="6" t="n">
+      <c r="Q25" s="6" t="n">
         <v>0.257</v>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="R25" s="6" t="n">
         <v>0.377</v>
       </c>
-      <c r="K25" s="6" t="n">
+      <c r="S25" s="6" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -1355,27 +1954,51 @@
         </is>
       </c>
       <c r="D26" s="6" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="H26" s="6" t="n">
         <v>0.198</v>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="I26" s="6" t="n">
         <v>0.2</v>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="J26" s="6" t="n">
         <v>0.482</v>
       </c>
-      <c r="G26" s="6" t="n">
+      <c r="K26" s="6" t="n">
         <v>0.188</v>
       </c>
-      <c r="H26" s="6" t="n">
+      <c r="L26" s="6" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="M26" s="6" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="N26" s="6" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="O26" s="6" t="n">
+        <v>0.181</v>
+      </c>
+      <c r="P26" s="6" t="n">
         <v>0.288</v>
       </c>
-      <c r="I26" s="6" t="n">
+      <c r="Q26" s="6" t="n">
         <v>0.257</v>
       </c>
-      <c r="J26" s="6" t="n">
+      <c r="R26" s="6" t="n">
         <v>0.377</v>
       </c>
-      <c r="K26" s="6" t="n">
+      <c r="S26" s="6" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -1388,27 +2011,51 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="H27" s="6" t="n">
         <v>0.198</v>
       </c>
-      <c r="E27" s="6" t="n">
+      <c r="I27" s="6" t="n">
         <v>0.2</v>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="J27" s="6" t="n">
         <v>0.482</v>
       </c>
-      <c r="G27" s="6" t="n">
+      <c r="K27" s="6" t="n">
         <v>0.188</v>
       </c>
-      <c r="H27" s="6" t="n">
+      <c r="L27" s="6" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="M27" s="6" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="N27" s="6" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="O27" s="6" t="n">
+        <v>0.181</v>
+      </c>
+      <c r="P27" s="6" t="n">
         <v>0.288</v>
       </c>
-      <c r="I27" s="6" t="n">
+      <c r="Q27" s="6" t="n">
         <v>0.257</v>
       </c>
-      <c r="J27" s="6" t="n">
+      <c r="R27" s="6" t="n">
         <v>0.377</v>
       </c>
-      <c r="K27" s="6" t="n">
+      <c r="S27" s="6" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -1429,27 +2076,51 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="H28" s="6" t="n">
         <v>0.05</v>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="I28" s="6" t="n">
         <v>0.038</v>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="J28" s="6" t="n">
         <v>0.517</v>
       </c>
-      <c r="G28" s="6" t="n">
+      <c r="K28" s="6" t="n">
         <v>0.202</v>
       </c>
-      <c r="H28" s="6" t="n">
+      <c r="L28" s="6" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="M28" s="6" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="N28" s="6" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="O28" s="6" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="P28" s="6" t="n">
         <v>0.108</v>
       </c>
-      <c r="I28" s="6" t="n">
+      <c r="Q28" s="6" t="n">
         <v>0.096</v>
       </c>
-      <c r="J28" s="6" t="n">
+      <c r="R28" s="6" t="n">
         <v>0.523</v>
       </c>
-      <c r="K28" s="6" t="n">
+      <c r="S28" s="6" t="n">
         <v>0.243</v>
       </c>
     </row>
@@ -1462,27 +2133,51 @@
         </is>
       </c>
       <c r="D29" s="6" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="H29" s="6" t="n">
         <v>0.08799999999999999</v>
       </c>
-      <c r="E29" s="6" t="n">
+      <c r="I29" s="6" t="n">
         <v>0.098</v>
       </c>
-      <c r="F29" s="6" t="n">
+      <c r="J29" s="6" t="n">
         <v>0.47</v>
       </c>
-      <c r="G29" s="6" t="n">
+      <c r="K29" s="6" t="n">
         <v>0.197</v>
       </c>
-      <c r="H29" s="6" t="n">
+      <c r="L29" s="6" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="M29" s="6" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="N29" s="6" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="O29" s="6" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="P29" s="6" t="n">
         <v>0.299</v>
       </c>
-      <c r="I29" s="6" t="n">
+      <c r="Q29" s="6" t="n">
         <v>0.366</v>
       </c>
-      <c r="J29" s="6" t="n">
+      <c r="R29" s="6" t="n">
         <v>0.434</v>
       </c>
-      <c r="K29" s="6" t="n">
+      <c r="S29" s="6" t="n">
         <v>0.177</v>
       </c>
     </row>
@@ -1495,27 +2190,51 @@
         </is>
       </c>
       <c r="D30" s="6" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="H30" s="6" t="n">
         <v>0.08799999999999999</v>
       </c>
-      <c r="E30" s="6" t="n">
+      <c r="I30" s="6" t="n">
         <v>0.098</v>
       </c>
-      <c r="F30" s="6" t="n">
+      <c r="J30" s="6" t="n">
         <v>0.47</v>
       </c>
-      <c r="G30" s="6" t="n">
+      <c r="K30" s="6" t="n">
         <v>0.197</v>
       </c>
-      <c r="H30" s="6" t="n">
+      <c r="L30" s="6" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="M30" s="6" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="N30" s="6" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="O30" s="6" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="P30" s="6" t="n">
         <v>0.299</v>
       </c>
-      <c r="I30" s="6" t="n">
+      <c r="Q30" s="6" t="n">
         <v>0.366</v>
       </c>
-      <c r="J30" s="6" t="n">
+      <c r="R30" s="6" t="n">
         <v>0.434</v>
       </c>
-      <c r="K30" s="6" t="n">
+      <c r="S30" s="6" t="n">
         <v>0.177</v>
       </c>
     </row>
@@ -1532,27 +2251,51 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="H31" s="6" t="n">
         <v>0.09</v>
       </c>
-      <c r="E31" s="6" t="n">
+      <c r="I31" s="6" t="n">
         <v>0.082</v>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="J31" s="6" t="n">
         <v>0.509</v>
       </c>
-      <c r="G31" s="6" t="n">
+      <c r="K31" s="6" t="n">
         <v>0.163</v>
       </c>
-      <c r="H31" s="6" t="n">
+      <c r="L31" s="6" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="M31" s="6" t="n">
+        <v>0.207</v>
+      </c>
+      <c r="N31" s="6" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="O31" s="6" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="P31" s="6" t="n">
         <v>0.301</v>
       </c>
-      <c r="I31" s="6" t="n">
+      <c r="Q31" s="6" t="n">
         <v>0.269</v>
       </c>
-      <c r="J31" s="6" t="n">
+      <c r="R31" s="6" t="n">
         <v>0.448</v>
       </c>
-      <c r="K31" s="6" t="n">
+      <c r="S31" s="6" t="n">
         <v>0.323</v>
       </c>
     </row>
@@ -1565,27 +2308,51 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>0.213</v>
+      </c>
+      <c r="H32" s="6" t="n">
         <v>0.135</v>
       </c>
-      <c r="E32" s="6" t="n">
+      <c r="I32" s="6" t="n">
         <v>0.149</v>
       </c>
-      <c r="F32" s="6" t="n">
+      <c r="J32" s="6" t="n">
         <v>0.519</v>
       </c>
-      <c r="G32" s="6" t="n">
+      <c r="K32" s="6" t="n">
         <v>0.179</v>
       </c>
-      <c r="H32" s="6" t="n">
+      <c r="L32" s="6" t="n">
+        <v>0.223</v>
+      </c>
+      <c r="M32" s="6" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="N32" s="6" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="O32" s="6" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="P32" s="6" t="n">
         <v>0.365</v>
       </c>
-      <c r="I32" s="6" t="n">
+      <c r="Q32" s="6" t="n">
         <v>0.362</v>
       </c>
-      <c r="J32" s="6" t="n">
+      <c r="R32" s="6" t="n">
         <v>0.408</v>
       </c>
-      <c r="K32" s="6" t="n">
+      <c r="S32" s="6" t="n">
         <v>0.264</v>
       </c>
     </row>
@@ -1598,27 +2365,51 @@
         </is>
       </c>
       <c r="D33" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>0.213</v>
+      </c>
+      <c r="H33" s="6" t="n">
         <v>0.135</v>
       </c>
-      <c r="E33" s="6" t="n">
+      <c r="I33" s="6" t="n">
         <v>0.149</v>
       </c>
-      <c r="F33" s="6" t="n">
+      <c r="J33" s="6" t="n">
         <v>0.519</v>
       </c>
-      <c r="G33" s="6" t="n">
+      <c r="K33" s="6" t="n">
         <v>0.179</v>
       </c>
-      <c r="H33" s="6" t="n">
+      <c r="L33" s="6" t="n">
+        <v>0.223</v>
+      </c>
+      <c r="M33" s="6" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="N33" s="6" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="O33" s="6" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="P33" s="6" t="n">
         <v>0.365</v>
       </c>
-      <c r="I33" s="6" t="n">
+      <c r="Q33" s="6" t="n">
         <v>0.362</v>
       </c>
-      <c r="J33" s="6" t="n">
+      <c r="R33" s="6" t="n">
         <v>0.408</v>
       </c>
-      <c r="K33" s="6" t="n">
+      <c r="S33" s="6" t="n">
         <v>0.264</v>
       </c>
     </row>
@@ -1650,25 +2441,25 @@
       <c r="G34" s="6" t="n">
         <v/>
       </c>
-      <c r="H34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="I34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="J34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="K34" s="6" t="n">
-        <v/>
-      </c>
+      <c r="H34" s="7" t="n"/>
+      <c r="I34" s="7" t="n"/>
+      <c r="J34" s="7" t="n"/>
+      <c r="K34" s="7" t="n"/>
+      <c r="L34" s="7" t="n"/>
+      <c r="M34" s="7" t="n"/>
+      <c r="N34" s="7" t="n"/>
+      <c r="O34" s="7" t="n"/>
+      <c r="P34" s="7" t="n"/>
+      <c r="Q34" s="7" t="n"/>
+      <c r="R34" s="7" t="n"/>
+      <c r="S34" s="7" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n"/>
       <c r="B35" s="5" t="n"/>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>ordered</t>
+          <t>ade</t>
         </is>
       </c>
       <c r="D35" s="6" t="n">
@@ -1684,16 +2475,40 @@
         <v/>
       </c>
       <c r="H35" s="6" t="n">
-        <v/>
+        <v>0.095</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v/>
+        <v>0.064</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v/>
+        <v>0.413</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v/>
+        <v>0.375</v>
+      </c>
+      <c r="L35" s="6" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="M35" s="6" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="N35" s="6" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="O35" s="6" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="P35" s="6" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="Q35" s="6" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="R35" s="6" t="n">
+        <v>0.514</v>
+      </c>
+      <c r="S35" s="6" t="n">
+        <v>0.261</v>
       </c>
     </row>
     <row r="36">
@@ -1701,7 +2516,7 @@
       <c r="B36" s="5" t="n"/>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>abde</t>
         </is>
       </c>
       <c r="D36" s="6" t="n">
@@ -1717,16 +2532,40 @@
         <v/>
       </c>
       <c r="H36" s="6" t="n">
-        <v/>
+        <v>0.109</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v/>
+        <v>0.08500000000000001</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v/>
+        <v>0.393</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v/>
+        <v>0.343</v>
+      </c>
+      <c r="L36" s="6" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="M36" s="6" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="N36" s="6" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="O36" s="6" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="P36" s="6" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="Q36" s="6" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="R36" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S36" s="6" t="n">
+        <v>0.218</v>
       </c>
     </row>
     <row r="37">
@@ -1734,7 +2573,7 @@
       <c r="B37" s="5" t="n"/>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>ade</t>
+          <t>abcde</t>
         </is>
       </c>
       <c r="D37" s="6" t="n">
@@ -1750,158 +2589,54 @@
         <v/>
       </c>
       <c r="H37" s="6" t="n">
-        <v/>
+        <v>0.109</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v/>
+        <v>0.08500000000000001</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v/>
+        <v>0.393</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="n"/>
-      <c r="B38" s="5" t="n"/>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>ab</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="E38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="F38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="G38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="H38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="I38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="J38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="K38" s="6" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="n"/>
-      <c r="B39" s="5" t="n"/>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>abde</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="E39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="F39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="G39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="H39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="I39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="J39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="K39" s="6" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="n"/>
-      <c r="B40" s="5" t="n"/>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>abc</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="E40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="F40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="G40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="H40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="I40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="J40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="K40" s="6" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="n"/>
-      <c r="B41" s="5" t="n"/>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>abcde</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="E41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="F41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="G41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="H41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="I41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="J41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="K41" s="6" t="n">
-        <v/>
+        <v>0.343</v>
+      </c>
+      <c r="L37" s="6" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="M37" s="6" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="N37" s="6" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="O37" s="6" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="P37" s="6" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="Q37" s="6" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="R37" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S37" s="6" t="n">
+        <v>0.218</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="8">
+    <mergeCell ref="H1:K1"/>
     <mergeCell ref="H2:K2"/>
+    <mergeCell ref="L2:O2"/>
+    <mergeCell ref="D1:G1"/>
     <mergeCell ref="D2:G2"/>
-    <mergeCell ref="H1:K1"/>
-    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="L1:O1"/>
+    <mergeCell ref="P1:S1"/>
+    <mergeCell ref="P2:S2"/>
   </mergeCells>
-  <conditionalFormatting sqref="D4:D41">
+  <conditionalFormatting sqref="D4:D37">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -1913,7 +2648,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E4:E41">
+  <conditionalFormatting sqref="E4:E37">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -1925,7 +2660,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F4:F41">
+  <conditionalFormatting sqref="F4:F37">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -1937,7 +2672,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G41">
+  <conditionalFormatting sqref="G4:G37">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -1949,7 +2684,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H41">
+  <conditionalFormatting sqref="H4:H37">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -1961,7 +2696,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I4:I41">
+  <conditionalFormatting sqref="I4:I37">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -1973,7 +2708,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J4:J41">
+  <conditionalFormatting sqref="J4:J37">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -1985,8 +2720,104 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K4:K41">
+  <conditionalFormatting sqref="K4:K37">
     <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L4:L37">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M4:M37">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N4:N37">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O4:O37">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P4:P37">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q4:Q37">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R4:R37">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8D7DA"/>
+        <color rgb="00FFF3CD"/>
+        <color rgb="00D4EDDA"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S4:S37">
+    <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
